--- a/output/第10期計画_給付実績データの受領点検.xlsx
+++ b/output/第10期計画_給付実績データの受領点検.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_給付費の実績と乖離" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_サービス別の実績" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_成果品への反映" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_支援ツールの実績値" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,7 +61,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +91,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,6 +225,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -778,16 +793,16 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="230" customHeight="1">
+    <row r="14" ht="200" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>受領した12ファイルの第1シート（給付費）には、次の個人情報が含まれています。
 　被保険者番号、氏名（カナ・漢字）、性別、生年月日、住民コード、世帯番号、行政区コード、住所コード、郵便番号
 行数は令和6年度57,142行、令和7年度59,576行です。
 受託者は、本業務の成果品には集計値のみを収録し、個票データを収録しない運用としています。本ファイルについても、集計シート（介護度別給付費、1月あたり利用者、1人1月あたり給付費、1人1月あたり利用回数）の値のみを用い、第1シートの個票は集計にも用いていません。
-つきましては、次の2点についてご確認をお願いします。
-① 個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は、次回以降は集計シートのみをご送付いただければ、個人情報を授受せずに作業できます。
-② 受託者における本ファイルの保管期間と廃棄の方法。ご指示がない場合は、業務終了後に消去し、消去の記録を残す取扱いといたします。</t>
+令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただきました。
+これを受け、集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去しました。
+なお、次回以降について、集計シートのみをご送付いただければ、個人情報を授受せずに同じ作業ができます。ご検討をお願いします。</t>
         </is>
       </c>
     </row>
@@ -4442,4 +4457,501 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>介護保険事業計画作成支援ツール　実績値シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和8年8月28日に3ファイル（町別）を受領しました。認定者数・介護サービス・保険料収納必要額の実績値です。第3段階（給付費・保険料）の算定に直接用います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>【1　ファイルと町の対応】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>受領したファイルには町名の記載がなく、ファイル名からも町を特定できませんでした。「介護サービス(実績値)」の施設・居住系の月平均利用者数を給付実績データの町別集計と突き合わせて特定しました。
+　東神楽町　特定22／GH33／地密特養18／特養44／老健23／医療院4
+　東川町　　特定27／GH32／地密特養 2／特養40／老健64／医療院2
+　美瑛町　　特定14／GH21／地密特養43／特養67／老健67／医療院3
+いずれも給付実績データの町別集計と一致します。この対応で相違ないかご確認をお願いします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>【2　第1号被保険者の認定者数】</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>所見</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>545</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>574</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>568</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>892</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>884</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>877</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>557</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>571</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>569</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>3町計</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>1994</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>見える化B系列による第1号認定者1,984人（令和8年3月末）と近い水準です。定義の対応は別途確認します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>【3　保険料収納必要額の構成要素（令和6年度）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>3町計</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>所見</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>施設サービスの食費</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>11559838</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>21537580</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>9055540</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>42152958</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>施設サービスの居住費</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>6178624</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>471272</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>7607001</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>14256897</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町が471,272円と、他町（618万円・761万円）に比べ小さい値です。施設の利用者数は美瑛町が最も多いため、ご確認をお願いします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>短期入所の食費</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>50986</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>18492717</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>268669</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>18812372</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町が18,492,717円と、他町（5万円・27万円）に比べ大きい値です。上記と併せてご確認をお願いします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>短期入所の居住費・滞在費</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>86508</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>560092</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>291619</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>938219</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>高額介護サービス費等</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>21223876</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>37852652</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>19610115</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>78686643</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>高額医療合算</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>2833254</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>3703668</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>2768907</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>9305829</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>算定対象審査支払手数料</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>649885</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>976214</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>680270</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>2306369</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>地域支援事業費</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>47544619</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>67561286</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>50625051</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>165730956</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち総合事業費</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>29630857</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>44256327</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>33242134</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>107129318</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち包括的支援事業等</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>17913762</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>23304959</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>17382917</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>58601638</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>市町村特別給付費等</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>3町とも0円です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>審査支払手数料の単価（円）</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="D27" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画値。3町とも68円です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>予定保険料収納率（％）</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>99</v>
+      </c>
+      <c r="C28" s="24" t="n">
+        <v>99</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <v>99</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画値。3町とも99％です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="110" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートにより、第3段階（給付費・保険料）の算定に必要な標準給付費の構成要素（特定入所者介護サービス費、高額介護サービス費、高額医療合算、審査支払手数料）、地域支援事業費、市町村特別給付費、予定保険料収納率が令和6年度の実績として得られました。
+注2）残るのは介護給付費準備基金の残高と積立・取崩実績（資料提供依頼No.9）、及び第10期の政令改正の内容（同No.11）です。
+注3）令和7年度・令和8年度の実績値シートは、認定者数と介護サービスの欄には値が入っていますが、保険料収納必要額の欄は令和6年度のみです。令和7年度分が確定しましたらご提供をお願いします。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_給付実績データの受領点検.xlsx
+++ b/output/第10期計画_給付実績データの受領点検.xlsx
@@ -619,7 +619,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年8月25日の進捗確認の打合せでご依頼した給付実績データ（資料提供依頼No.23）を、令和8年8月28日に12ファイル受領しました。内容を点検した結果を示します。</t>
+          <t>令和8年8月26日の進捗確認の打合せでご依頼した給付実績データ（資料提供依頼No.23）を、令和8年8月28日に12ファイル受領しました。内容を点検した結果を示します。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_給付実績データの受領点検.xlsx
+++ b/output/第10期計画_給付実績データの受領点検.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_サービス別の実績" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_成果品への反映" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_支援ツールの実績値" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_収録項目の範囲" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -169,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,6 +235,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4954,4 +4958,622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>受領ファイルの収録項目の範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>代表KPI H16（業務継続計画を策定している事業所の割合）を給付実績から算定できるかを確かめるため、受領した12ファイルの収録項目を点検しました。結果として、加算・減算の内訳は収録されていません。点検日：令和8年9月4日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>点検した事項</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>点検の方法</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>給付費シートの列構成</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>第1シート（給付費）の見出し行を読み、収録されている項目を列挙した。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>125項目である。被保険者・認定・事業所・サービス種類・日数回数・単位数・請求額・公費・食事提供費・特定入所者介護サービス費・社会福祉法人軽減までを収録している。最も細かい単位はサービス種類コード（第39列）であり、サービス項目コード（加算・減算の単位）の列はない。</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>サービス種類単位</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>加算・減算の有無</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>12ファイルすべての共有文字列（xl/sharedStrings.xml）を取り出し、「減算」「加算」「業務継続」「ＢＣＰ」「BCP」「サービス項目」「サービスコード」を検索した。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>12ファイルとも、いずれの語も0件である。共有文字列の総数は令和6・7年度が7,567〜7,605、令和8年度が5,573〜5,574である。</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>収録なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>H16の算定可否</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>業務継続計画未策定減算の算定状況を受領ファイルから抽出できるかを判定した。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>抽出できない。減算は請求明細書のサービス項目コードにより識別されるが、受領ファイルはサービス種類コードまでの集約である。国民健康保険団体連合会の給付実績（明細情報）の抽出を要する。</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>算定できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>交付金の評価指標による代替</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度 保険者機能強化推進交付金等に係る評価指標（42頁・全文37,721字）を全文検索した。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>「業務継続」「継続計画」「災害」「感染症」「ＢＣＰ」「BCP」はいずれも0件である。交付金の評価指標に業務継続計画に関する項目はない。</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>代替できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス情報公表システムによる代替</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>受託者が収集した公表画面の項目（30項目）及び北海道が加工したオープンデータ（9項目）を点検した。</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>業務継続計画に関する項目はない。</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>代替できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>【受領ファイル12件の点検結果】</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ファイル</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>共有文字列</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>減算</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>加算</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>業務継続・ＢＣＰ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>【大雪】R6.給付費データ集計.xlsx</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>7605</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>【大雪】R7.給付費データ集計.xlsx</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>7568</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>【大雪】R8.給付費データ集計.xlsx</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>5574</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>【東川町】R6.給付費データ.xlsx</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>7604</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>【東川町】R7.給付費データ.xlsx</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>7567</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>【東川町】R8.給付費データ.xlsx</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>5574</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>【美瑛町】R6.給付費データ.xlsx</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>7604</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>【美瑛町】R7.給付費データ.xlsx</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>7568</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>【美瑛町】R8.給付費データ.xlsx</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>5573</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>【東神楽町】R6.給付費データ.xlsx</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>7604</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>【東神楽町】R7.給付費データ.xlsx</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>7568</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>【東神楽町】R8.給付費データ.xlsx</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>5573</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>【H16の取扱い（受託者案）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>結論</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>追加提供資料が見込めない前提では、H16は算定できない。代表KPIの優先順位（内部確認結果への対応整理 09シート）で優先度Dとし、指標から外す。</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>追加提供が得られる場合</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>国民健康保険団体連合会の給付実績（明細情報）から業務継続計画未策定減算を算定した事業所を抽出できれば、毎年度算定でき、優先度Bへ上がる。抽出の可否を確認事項として掲げる。</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>追加提供を要しない代替</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>広域連合は地域密着型サービスの指定権者であり、指定・更新・運営指導の際に業務継続計画の策定状況を確認できる。区域内の地域密着型サービス事業所は17事業所（東川町4・美瑛町10・東神楽町3）である。第5章基本目標5のアウトプットとして「指定・更新・運営指導の際に業務継続計画の策定を確認した地域密着型サービス事業所の数」を置く。</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>広域型の扱い</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム・介護老人保健施設・訪問介護等の指定権者は北海道である。広域型の策定状況は北海道の指導監査の結果によるため、広域連合の指標には含めない。</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="110" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートは、令和8年9月3日の内部確認結果を受けた代表KPIの再整理に伴う点検です。「受領済みの給付費データにH16の根拠が含まれているか」を確かめたものです。
+注2）点検は受領ファイルの共有文字列を機械的に検索する方法により、12ファイルすべてを対象としています。個票の内容そのものは読み取っていません。
+注3）受領ファイルには氏名・生年月日・住所コード等の個票が含まれるため、本表には収録していません。個人情報は保管せず廃棄する方針によります。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A33:E33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>